--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
     </row>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
     </row>
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -13258,22 +13258,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13283,29 +13283,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13315,29 +13315,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13347,29 +13347,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
@@ -13396,12 +13396,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13411,29 +13411,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
@@ -13455,17 +13455,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13487,17 +13487,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13507,29 +13507,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13539,29 +13539,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13571,29 +13571,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13603,29 +13603,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13635,29 +13635,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
@@ -13679,17 +13679,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13699,29 +13699,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13731,29 +13731,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13763,29 +13763,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13795,29 +13795,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
@@ -13839,17 +13839,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13859,14 +13859,14 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -13876,12 +13876,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -13903,17 +13903,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13923,29 +13923,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13955,29 +13955,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13987,29 +13987,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -14031,17 +14031,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -14063,17 +14063,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14083,29 +14083,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14115,29 +14115,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -14159,17 +14159,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14179,29 +14179,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14211,29 +14211,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14243,29 +14243,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14275,29 +14275,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14307,29 +14307,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
@@ -14351,17 +14351,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
@@ -14415,17 +14415,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14435,29 +14435,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14467,29 +14467,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14499,29 +14499,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
@@ -14570,22 +14570,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14607,17 +14607,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14627,29 +14627,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14671,17 +14671,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14703,17 +14703,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14730,22 +14730,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14767,17 +14767,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14799,17 +14799,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14826,22 +14826,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14863,17 +14863,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14895,17 +14895,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14922,22 +14922,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14959,17 +14959,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14986,22 +14986,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -15023,17 +15023,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15055,17 +15055,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15082,22 +15082,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15114,22 +15114,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15151,17 +15151,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15178,22 +15178,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15210,22 +15210,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15274,22 +15274,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15311,17 +15311,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15338,22 +15338,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•吉林南山街</t>
+          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
+          <t>鸿蒙智行授权用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
     </row>
@@ -13258,22 +13258,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13283,29 +13283,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13315,29 +13315,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13347,29 +13347,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13379,29 +13379,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13411,29 +13411,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13443,29 +13443,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
@@ -13487,17 +13487,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13507,29 +13507,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13539,29 +13539,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13571,29 +13571,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13603,29 +13603,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
@@ -13647,17 +13647,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13667,29 +13667,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13699,29 +13699,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -13743,17 +13743,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
@@ -13775,17 +13775,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
@@ -13807,17 +13807,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13827,29 +13827,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13859,29 +13859,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13891,29 +13891,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13923,29 +13923,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13955,29 +13955,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -13999,17 +13999,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14019,29 +14019,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14051,29 +14051,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
         </is>
       </c>
     </row>
@@ -14095,17 +14095,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14115,29 +14115,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -14159,17 +14159,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14179,29 +14179,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14211,14 +14211,14 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14243,29 +14243,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14275,29 +14275,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -14319,17 +14319,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14339,29 +14339,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14371,29 +14371,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14403,29 +14403,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14435,29 +14435,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14467,29 +14467,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14499,29 +14499,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14563,29 +14563,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14595,29 +14595,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14639,17 +14639,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14671,17 +14671,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14698,22 +14698,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14730,22 +14730,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14767,17 +14767,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14799,17 +14799,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14831,17 +14831,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14863,17 +14863,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14890,22 +14890,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14922,22 +14922,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14959,17 +14959,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14991,17 +14991,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -15023,17 +15023,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15055,17 +15055,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15082,7 +15082,7 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -15092,12 +15092,12 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15114,22 +15114,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15151,17 +15151,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15178,22 +15178,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15210,22 +15210,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15242,22 +15242,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15279,17 +15279,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15311,17 +15311,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15338,22 +15338,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
+          <t>鸿蒙智行授权用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•吉林南山街</t>
+          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -13258,22 +13258,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13283,29 +13283,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13315,29 +13315,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13347,29 +13347,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
         </is>
       </c>
     </row>
@@ -13391,17 +13391,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13411,29 +13411,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13443,29 +13443,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -13514,22 +13514,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13539,29 +13539,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13571,29 +13571,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
@@ -13615,17 +13615,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13635,29 +13635,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
@@ -13706,22 +13706,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13731,29 +13731,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13763,29 +13763,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
@@ -13807,17 +13807,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13827,29 +13827,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13859,29 +13859,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13891,29 +13891,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
@@ -13935,17 +13935,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13955,29 +13955,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
@@ -13999,17 +13999,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14019,14 +14019,14 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -14036,12 +14036,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -14063,17 +14063,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14083,29 +14083,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14115,29 +14115,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14147,29 +14147,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14179,29 +14179,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
@@ -14223,17 +14223,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14243,29 +14243,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14275,29 +14275,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14307,29 +14307,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
@@ -14351,17 +14351,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
@@ -14383,17 +14383,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14403,29 +14403,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14435,29 +14435,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
@@ -14479,17 +14479,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -14511,17 +14511,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
@@ -14602,22 +14602,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14627,29 +14627,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14659,29 +14659,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14698,22 +14698,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14730,22 +14730,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14767,17 +14767,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14799,17 +14799,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14831,17 +14831,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14863,17 +14863,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14890,22 +14890,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14927,17 +14927,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14959,17 +14959,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14991,17 +14991,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -15018,22 +15018,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15055,17 +15055,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15082,22 +15082,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15119,17 +15119,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15151,17 +15151,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15178,22 +15178,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15210,22 +15210,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15242,22 +15242,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15279,17 +15279,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15306,22 +15306,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15338,22 +15338,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（55家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（59家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（55家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（59家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•吉林南山街</t>
+          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
+          <t>鸿蒙智行授权用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
     </row>
@@ -13258,22 +13258,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13283,29 +13283,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -13354,22 +13354,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13379,29 +13379,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13411,29 +13411,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13443,29 +13443,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13475,29 +13475,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13507,29 +13507,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13539,29 +13539,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
@@ -13615,17 +13615,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13635,29 +13635,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13667,29 +13667,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13699,29 +13699,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -13775,17 +13775,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13795,29 +13795,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
         </is>
       </c>
     </row>
@@ -13839,17 +13839,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13859,29 +13859,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13891,29 +13891,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13923,29 +13923,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -13967,17 +13967,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13987,29 +13987,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14019,29 +14019,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14051,29 +14051,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14083,29 +14083,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14115,29 +14115,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14147,29 +14147,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -14191,17 +14191,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14211,29 +14211,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14243,29 +14243,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
@@ -14287,17 +14287,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14307,29 +14307,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14339,29 +14339,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
@@ -14410,22 +14410,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
@@ -14447,17 +14447,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14467,29 +14467,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14499,29 +14499,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14563,29 +14563,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14607,17 +14607,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14627,29 +14627,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14659,29 +14659,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14703,17 +14703,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14730,22 +14730,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14767,17 +14767,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14799,17 +14799,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14831,17 +14831,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14863,17 +14863,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14890,22 +14890,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14927,17 +14927,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14954,7 +14954,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -14964,12 +14964,12 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14991,17 +14991,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -15018,22 +15018,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15050,22 +15050,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15082,22 +15082,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15119,17 +15119,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15146,22 +15146,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15183,17 +15183,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15215,17 +15215,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15242,22 +15242,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15279,17 +15279,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15306,22 +15306,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15338,22 +15338,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（55家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（59家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（55家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（59家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
+          <t>鸿蒙智行授权用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•吉林南山街</t>
+          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
     </row>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
     </row>
@@ -13263,17 +13263,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13283,29 +13283,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13315,29 +13315,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13347,29 +13347,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13379,29 +13379,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13411,29 +13411,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
@@ -13487,17 +13487,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
@@ -13519,17 +13519,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13551,17 +13551,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13571,29 +13571,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13603,29 +13603,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13635,29 +13635,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13667,29 +13667,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13699,29 +13699,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13731,29 +13731,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13763,29 +13763,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -13839,17 +13839,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13859,29 +13859,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13891,29 +13891,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13923,29 +13923,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13955,29 +13955,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13987,29 +13987,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14019,29 +14019,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14051,29 +14051,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
         </is>
       </c>
     </row>
@@ -14095,17 +14095,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14115,29 +14115,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14147,29 +14147,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
         </is>
       </c>
     </row>
@@ -14191,17 +14191,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14211,29 +14211,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14243,29 +14243,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14275,29 +14275,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14307,29 +14307,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14339,29 +14339,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
@@ -14383,17 +14383,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -14415,17 +14415,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -14447,17 +14447,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14467,29 +14467,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14499,29 +14499,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14607,17 +14607,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
@@ -14644,12 +14644,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14659,29 +14659,29 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14698,22 +14698,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14735,17 +14735,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14767,17 +14767,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14799,17 +14799,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14831,17 +14831,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14858,22 +14858,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14890,22 +14890,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14927,17 +14927,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14954,22 +14954,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14986,22 +14986,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -15023,17 +15023,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15050,22 +15050,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15087,17 +15087,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15119,17 +15119,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15146,22 +15146,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15183,17 +15183,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15215,17 +15215,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15242,22 +15242,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15279,17 +15279,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15306,22 +15306,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15338,22 +15338,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（55家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（59家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（55家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（59家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
     </row>
@@ -13263,17 +13263,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13283,29 +13283,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13315,29 +13315,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13347,29 +13347,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13379,29 +13379,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -13423,17 +13423,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
         </is>
       </c>
     </row>
@@ -13455,17 +13455,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13475,29 +13475,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
@@ -13519,17 +13519,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
@@ -13551,17 +13551,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13603,29 +13603,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13635,29 +13635,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
@@ -13706,22 +13706,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13731,29 +13731,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13763,29 +13763,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13795,29 +13795,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
@@ -13839,17 +13839,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13859,29 +13859,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13891,29 +13891,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
@@ -13935,17 +13935,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13955,29 +13955,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
@@ -14026,22 +14026,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
@@ -14063,17 +14063,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14083,14 +14083,14 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -14100,12 +14100,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14115,29 +14115,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
@@ -14186,22 +14186,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
@@ -14223,17 +14223,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14243,7 +14243,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
@@ -14255,17 +14255,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14275,29 +14275,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
@@ -14319,17 +14319,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14339,29 +14339,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -14383,17 +14383,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
@@ -14415,17 +14415,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14435,29 +14435,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14467,29 +14467,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -14511,17 +14511,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14639,17 +14639,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14659,14 +14659,14 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -14676,12 +14676,12 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14698,22 +14698,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14730,22 +14730,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14762,22 +14762,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14799,17 +14799,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14831,17 +14831,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14858,22 +14858,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14895,17 +14895,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14927,17 +14927,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14959,17 +14959,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14986,22 +14986,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -15023,17 +15023,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15055,17 +15055,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15087,17 +15087,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15119,17 +15119,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15146,22 +15146,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15183,17 +15183,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15210,7 +15210,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15242,22 +15242,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15279,17 +15279,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15306,22 +15306,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15343,17 +15343,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（55家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（59家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（55家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（59家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•吉林南山街</t>
+          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
+          <t>鸿蒙智行授权用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
     </row>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
     </row>
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -13258,22 +13258,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13283,7 +13283,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -13295,17 +13295,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13315,29 +13315,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13347,29 +13347,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
@@ -13391,17 +13391,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13411,14 +13411,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -13428,12 +13428,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -13455,17 +13455,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
@@ -13487,17 +13487,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13507,14 +13507,14 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -13524,12 +13524,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
@@ -13551,17 +13551,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13571,29 +13571,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13603,29 +13603,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -13647,17 +13647,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13667,29 +13667,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13699,29 +13699,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13731,29 +13731,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13763,29 +13763,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13795,29 +13795,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13827,29 +13827,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13859,29 +13859,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13891,29 +13891,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13923,29 +13923,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13955,29 +13955,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13987,29 +13987,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14019,29 +14019,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -14063,17 +14063,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14083,29 +14083,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14115,29 +14115,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -14159,17 +14159,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14179,29 +14179,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14211,29 +14211,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14243,29 +14243,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14275,29 +14275,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -14319,17 +14319,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14339,29 +14339,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -14410,22 +14410,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -14447,17 +14447,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14467,29 +14467,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14499,29 +14499,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
@@ -14570,22 +14570,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14595,29 +14595,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14639,17 +14639,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
@@ -14671,17 +14671,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14703,17 +14703,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14730,22 +14730,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14762,22 +14762,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14799,17 +14799,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14831,17 +14831,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14858,22 +14858,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14890,22 +14890,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14927,17 +14927,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14959,17 +14959,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14986,22 +14986,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -15023,17 +15023,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15055,17 +15055,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15087,17 +15087,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15114,22 +15114,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15146,22 +15146,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15178,22 +15178,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15210,22 +15210,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15242,22 +15242,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15279,17 +15279,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15306,22 +15306,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15343,17 +15343,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
+          <t>鸿蒙智行授权用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•吉林南山街</t>
+          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
     </row>
@@ -13258,22 +13258,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13283,29 +13283,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13315,29 +13315,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13347,29 +13347,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -13391,17 +13391,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13411,29 +13411,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13443,29 +13443,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
@@ -13487,17 +13487,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13507,29 +13507,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13539,29 +13539,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13603,29 +13603,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13635,29 +13635,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13667,29 +13667,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
         </is>
       </c>
     </row>
@@ -13711,17 +13711,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13731,29 +13731,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13763,29 +13763,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
@@ -13807,17 +13807,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
@@ -13839,17 +13839,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13859,29 +13859,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13891,29 +13891,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13923,29 +13923,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13955,29 +13955,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13987,29 +13987,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14019,29 +14019,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -14063,17 +14063,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
@@ -14095,17 +14095,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14115,29 +14115,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14147,29 +14147,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14179,29 +14179,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14211,29 +14211,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14243,29 +14243,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -14287,17 +14287,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
@@ -14319,17 +14319,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14339,29 +14339,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14371,29 +14371,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14403,29 +14403,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -14447,17 +14447,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14467,29 +14467,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14499,29 +14499,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14563,29 +14563,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14595,29 +14595,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
@@ -14644,12 +14644,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14671,17 +14671,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14703,17 +14703,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14735,17 +14735,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14762,22 +14762,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14799,17 +14799,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14831,17 +14831,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14863,17 +14863,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14890,22 +14890,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14922,22 +14922,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14959,17 +14959,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14986,22 +14986,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -15055,17 +15055,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15087,17 +15087,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15114,22 +15114,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15146,22 +15146,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15178,22 +15178,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15215,17 +15215,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15242,22 +15242,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15274,22 +15274,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15306,22 +15306,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15343,17 +15343,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8719</v>
+        <v>8721</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8715</v>
+        <v>8717</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-4</v>
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E434"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6507,14 +6507,14 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="2" t="n">
         <v>0</v>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="2" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="2" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="2" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="2" t="n">
@@ -6612,101 +6612,101 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C272" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E272" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="4" t="inlineStr">
+      <c r="C274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B273" s="4" t="inlineStr">
+      <c r="B275" s="4" t="inlineStr">
         <is>
           <t>山东</t>
         </is>
       </c>
-      <c r="C273" s="4" t="n">
+      <c r="C275" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D273" s="4" t="n">
+      <c r="D275" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="E273" s="4" t="n">
+      <c r="E275" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="4" t="inlineStr">
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B274" s="4" t="inlineStr">
+      <c r="B276" s="4" t="inlineStr">
         <is>
           <t>福建</t>
         </is>
       </c>
-      <c r="C274" s="4" t="n">
+      <c r="C276" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="D274" s="4" t="n">
+      <c r="D276" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="E274" s="4" t="n">
+      <c r="E276" s="4" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D275" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E275" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B276" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C276" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D276" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E276" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -6717,14 +6717,14 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C277" s="2" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E277" s="2" t="n">
         <v>0</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C278" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E278" s="2" t="n">
         <v>0</v>
@@ -6759,14 +6759,14 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C279" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E279" s="2" t="n">
         <v>0</v>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C280" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E280" s="2" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C281" s="2" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E281" s="2" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E282" s="2" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E283" s="2" t="n">
         <v>0</v>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C284" s="2" t="n">
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E285" s="2" t="n">
         <v>0</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C286" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E286" s="2" t="n">
         <v>0</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C287" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E287" s="2" t="n">
         <v>0</v>
@@ -6948,14 +6948,14 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C288" s="2" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="E288" s="2" t="n">
         <v>0</v>
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E289" s="2" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="E290" s="2" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E291" s="2" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E292" s="2" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E293" s="2" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C294" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E294" s="2" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C295" s="2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E295" s="2" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E296" s="2" t="n">
         <v>0</v>
@@ -7137,59 +7137,59 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D297" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D298" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C297" s="2" t="n">
+      <c r="C299" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D297" s="2" t="n">
+      <c r="D299" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E297" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B298" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C298" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="D298" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="E298" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B299" s="3" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C299" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="D299" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="E299" s="3" t="n">
-        <v>1</v>
+      <c r="E299" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -7200,14 +7200,14 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="D300" s="3" t="n">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="E300" s="3" t="n">
         <v>1</v>
@@ -7221,14 +7221,14 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D301" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E301" s="3" t="n">
         <v>1</v>
@@ -7242,59 +7242,59 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D302" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="E302" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D303" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E303" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
           <t>江苏</t>
         </is>
       </c>
-      <c r="C302" s="3" t="n">
+      <c r="C304" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="D302" s="3" t="n">
+      <c r="D304" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="E302" s="3" t="n">
+      <c r="E304" s="3" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="4" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B303" s="4" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C303" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="D303" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="E303" s="4" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="4" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B304" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C304" s="4" t="n">
-        <v>136</v>
-      </c>
-      <c r="D304" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="E304" s="4" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="305">
@@ -7305,14 +7305,14 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C305" s="4" t="n">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="D305" s="4" t="n">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="E305" s="4" t="n">
         <v>-3</v>
@@ -7326,17 +7326,17 @@
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C306" s="4" t="n">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="D306" s="4" t="n">
-        <v>45</v>
+        <v>133</v>
       </c>
       <c r="E306" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="307">
@@ -7347,17 +7347,17 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C307" s="4" t="n">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="D307" s="4" t="n">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="E307" s="4" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="308">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C308" s="4" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D308" s="4" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E308" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="309">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C309" s="4" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="D309" s="4" t="n">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="E309" s="4" t="n">
         <v>-1</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C310" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D310" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E310" s="4" t="n">
         <v>-1</v>
@@ -7431,59 +7431,59 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C311" s="4" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="D311" s="4" t="n">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="E311" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="inlineStr">
+      <c r="A312" s="4" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B312" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C312" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D312" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E312" s="2" t="n">
-        <v>0</v>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D312" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="E312" s="4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="inlineStr">
+      <c r="A313" s="4" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B313" s="2" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C313" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D313" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="E313" s="2" t="n">
-        <v>0</v>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="D313" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="E313" s="4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="314">
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C314" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E314" s="2" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C315" s="2" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E315" s="2" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E316" s="2" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E317" s="2" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E318" s="2" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="E319" s="2" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C320" s="2" t="n">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="E320" s="2" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="E321" s="2" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E322" s="2" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E323" s="2" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C324" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E324" s="2" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C325" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E325" s="2" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C326" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E326" s="2" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C327" s="2" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E327" s="2" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C328" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E328" s="2" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C329" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E329" s="2" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C330" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E330" s="2" t="n">
         <v>0</v>
@@ -7851,143 +7851,143 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D331" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E331" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D332" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E332" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
           <t>青海</t>
         </is>
       </c>
-      <c r="C331" s="2" t="n">
+      <c r="C333" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D331" s="2" t="n">
+      <c r="D333" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E331" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="3" t="inlineStr">
+      <c r="E333" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B332" s="3" t="inlineStr">
+      <c r="B334" s="3" t="inlineStr">
         <is>
           <t>吉林</t>
         </is>
       </c>
-      <c r="C332" s="3" t="n">
+      <c r="C334" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D332" s="3" t="n">
+      <c r="D334" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="E332" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="3" t="inlineStr">
+      <c r="E334" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B333" s="3" t="inlineStr">
+      <c r="B335" s="3" t="inlineStr">
         <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C333" s="3" t="n">
+      <c r="C335" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D333" s="3" t="n">
+      <c r="D335" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="E333" s="3" t="n">
+      <c r="E335" s="3" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" s="4" t="inlineStr">
+    <row r="336">
+      <c r="A336" s="4" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B334" s="4" t="inlineStr">
+      <c r="B336" s="4" t="inlineStr">
         <is>
           <t>安徽</t>
         </is>
       </c>
-      <c r="C334" s="4" t="n">
+      <c r="C336" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D334" s="4" t="n">
+      <c r="D336" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="E334" s="4" t="n">
+      <c r="E336" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" s="4" t="inlineStr">
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B335" s="4" t="inlineStr">
+      <c r="B337" s="4" t="inlineStr">
         <is>
           <t>湖北</t>
         </is>
       </c>
-      <c r="C335" s="4" t="n">
+      <c r="C337" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="D335" s="4" t="n">
+      <c r="D337" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E335" s="4" t="n">
+      <c r="E337" s="4" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B336" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C336" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="D336" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="E336" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B337" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C337" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D337" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E337" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C338" s="2" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E338" s="2" t="n">
         <v>0</v>
@@ -8019,14 +8019,14 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C339" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E339" s="2" t="n">
         <v>0</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E341" s="2" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D343" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E343" s="2" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C346" s="2" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="D346" s="2" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="E346" s="2" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E347" s="2" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="D348" s="2" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="E348" s="2" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="E349" s="2" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E350" s="2" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C351" s="2" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="E351" s="2" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C352" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E352" s="2" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C353" s="2" t="n">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="D353" s="2" t="n">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="E353" s="2" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C354" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D354" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E354" s="2" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C355" s="2" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="D355" s="2" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="E355" s="2" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C356" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D356" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E356" s="2" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C357" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D357" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E357" s="2" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C358" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D358" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E358" s="2" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C359" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E359" s="2" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C360" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D360" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E360" s="2" t="n">
         <v>0</v>
@@ -8481,14 +8481,14 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E361" s="2" t="n">
         <v>0</v>
@@ -8502,49 +8502,49 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C362" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D362" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E362" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="3" t="inlineStr">
+      <c r="A363" s="2" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B363" s="3" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C363" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D363" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="E363" s="3" t="n">
-        <v>1</v>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D363" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E363" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C364" s="2" t="n">
@@ -8558,24 +8558,24 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B365" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C365" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D365" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E365" s="2" t="n">
-        <v>0</v>
+      <c r="A365" s="3" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C365" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D365" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E365" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C366" s="2" t="n">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C367" s="2" t="n">
@@ -8628,14 +8628,14 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D368" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E368" s="2" t="n">
         <v>0</v>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
@@ -8670,14 +8670,14 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D370" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E370" s="2" t="n">
         <v>0</v>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C371" s="2" t="n">
@@ -8712,14 +8712,14 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C372" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D372" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E372" s="2" t="n">
         <v>0</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C373" s="2" t="n">
@@ -8749,19 +8749,19 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D374" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E374" s="2" t="n">
         <v>0</v>
@@ -8770,19 +8770,19 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C375" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D375" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E375" s="2" t="n">
         <v>0</v>
@@ -8796,14 +8796,14 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C376" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D376" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E376" s="2" t="n">
         <v>0</v>
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C377" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D377" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E377" s="2" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E378" s="2" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C379" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D379" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E379" s="2" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E380" s="2" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C381" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D381" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E381" s="2" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C382" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E382" s="2" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C383" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D383" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E383" s="2" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C384" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D384" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E384" s="2" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C385" s="2" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="D385" s="2" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="E385" s="2" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C386" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D386" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E386" s="2" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C387" s="2" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D387" s="2" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="E387" s="2" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C388" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D388" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E388" s="2" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C389" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D389" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E389" s="2" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C390" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D390" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E390" s="2" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C391" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D391" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E391" s="2" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C392" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D392" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E392" s="2" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C393" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D393" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E393" s="2" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C394" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D394" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E394" s="2" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C395" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D395" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E395" s="2" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C396" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D396" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E396" s="2" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C397" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D397" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E397" s="2" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C398" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D398" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E398" s="2" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C399" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D399" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E399" s="2" t="n">
         <v>0</v>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C400" s="2" t="n">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C401" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D401" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E401" s="2" t="n">
         <v>0</v>
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D402" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E402" s="2" t="n">
         <v>0</v>
@@ -9363,59 +9363,59 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D403" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C403" s="2" t="n">
+      <c r="C405" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D403" s="2" t="n">
+      <c r="D405" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E403" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B404" s="4" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C404" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="D404" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="E404" s="4" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="4" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C405" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="D405" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="E405" s="4" t="n">
-        <v>-2</v>
+      <c r="E405" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -9426,17 +9426,17 @@
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C406" s="4" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D406" s="4" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="E406" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="407">
@@ -9447,17 +9447,17 @@
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C407" s="4" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D407" s="4" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E407" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="408">
@@ -9468,14 +9468,14 @@
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C408" s="4" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D408" s="4" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="E408" s="4" t="n">
         <v>-1</v>
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C409" s="4" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D409" s="4" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E409" s="4" t="n">
         <v>-1</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C410" s="4" t="n">
-        <v>151</v>
+        <v>24</v>
       </c>
       <c r="D410" s="4" t="n">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="E410" s="4" t="n">
         <v>-1</v>
@@ -9531,59 +9531,59 @@
       </c>
       <c r="B411" s="4" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C411" s="4" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D411" s="4" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E411" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="inlineStr">
+      <c r="A412" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B412" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C412" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D412" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="E412" s="2" t="n">
-        <v>0</v>
+      <c r="B412" s="4" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="C412" s="4" t="n">
+        <v>151</v>
+      </c>
+      <c r="D412" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E412" s="4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="inlineStr">
+      <c r="A413" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B413" s="2" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C413" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="D413" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="E413" s="2" t="n">
-        <v>0</v>
+      <c r="B413" s="4" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C413" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D413" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="E413" s="4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="414">
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D414" s="2" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D415" s="2" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="E415" s="2" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>204</v>
+        <v>13</v>
       </c>
       <c r="D416" s="2" t="n">
-        <v>204</v>
+        <v>13</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D417" s="2" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>60</v>
+        <v>204</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>60</v>
+        <v>204</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D420" s="2" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E420" s="2" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D424" s="2" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D425" s="2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="D426" s="2" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E426" s="2" t="n">
         <v>0</v>
@@ -9867,59 +9867,59 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="D427" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="E427" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D428" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E428" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C427" s="2" t="n">
+      <c r="C429" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D427" s="2" t="n">
+      <c r="D429" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E427" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B428" s="3" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C428" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="D428" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="E428" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B429" s="3" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C429" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="D429" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="E429" s="3" t="n">
-        <v>1</v>
+      <c r="E429" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="430">
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C430" s="3" t="n">
-        <v>144</v>
+        <v>33</v>
       </c>
       <c r="D430" s="3" t="n">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="E430" s="3" t="n">
         <v>1</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C431" s="3" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="D431" s="3" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="E431" s="3" t="n">
         <v>1</v>
@@ -9972,17 +9972,17 @@
       </c>
       <c r="B432" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C432" s="3" t="n">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="D432" s="3" t="n">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="E432" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
@@ -9993,17 +9993,17 @@
       </c>
       <c r="B433" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C433" s="3" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="D433" s="3" t="n">
-        <v>102</v>
+        <v>20</v>
       </c>
       <c r="E433" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
@@ -10014,16 +10014,58 @@
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="C434" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D434" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E434" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B435" s="3" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C435" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D435" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="E435" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
           <t>湖南</t>
         </is>
       </c>
-      <c r="C434" s="3" t="n">
+      <c r="C436" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="D434" s="3" t="n">
+      <c r="D436" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E434" s="3" t="n">
+      <c r="E436" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11163,7 +11205,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•吉林南山街</t>
+          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11190,7 +11232,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
+          <t>鸿蒙智行授权用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12480,7 +12522,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12495,7 +12537,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12549,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12522,7 +12564,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12576,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12549,7 +12591,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
     </row>
@@ -13263,17 +13305,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13283,29 +13325,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13315,29 +13357,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13347,7 +13389,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
@@ -13364,12 +13406,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13379,29 +13421,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13411,29 +13453,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13443,29 +13485,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13475,7 +13517,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
@@ -13487,17 +13529,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13507,29 +13549,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13539,29 +13581,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13571,7 +13613,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
@@ -13610,22 +13652,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13635,29 +13677,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13667,29 +13709,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13699,29 +13741,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13731,29 +13773,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13763,29 +13805,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13795,29 +13837,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13827,29 +13869,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13859,29 +13901,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13891,7 +13933,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
@@ -13903,17 +13945,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13923,29 +13965,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13955,29 +13997,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13987,7 +14029,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -13999,17 +14041,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14019,29 +14061,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14051,29 +14093,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14083,29 +14125,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14115,7 +14157,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -14127,17 +14169,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14147,29 +14189,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14179,29 +14221,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14211,7 +14253,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
@@ -14223,17 +14265,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14243,7 +14285,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
         </is>
       </c>
     </row>
@@ -14255,17 +14297,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14275,29 +14317,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14307,7 +14349,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
@@ -14319,17 +14361,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14339,7 +14381,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -14351,17 +14393,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14371,29 +14413,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14403,29 +14445,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14435,7 +14477,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -14447,17 +14489,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14467,29 +14509,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14499,29 +14541,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14531,7 +14573,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -14570,22 +14612,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14595,7 +14637,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14634,22 +14676,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14659,7 +14701,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14671,17 +14713,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14703,17 +14745,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14735,17 +14777,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14762,22 +14804,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14794,22 +14836,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14831,17 +14873,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14863,17 +14905,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14895,17 +14937,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14922,22 +14964,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14959,17 +15001,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14986,22 +15028,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -15018,22 +15060,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15050,22 +15092,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15087,17 +15129,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15114,22 +15156,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15146,22 +15188,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15183,17 +15225,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15215,17 +15257,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15247,17 +15289,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15274,22 +15316,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15306,22 +15348,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15343,17 +15385,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（55家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（59家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（55家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（59家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
     </row>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
+          <t>鸿蒙智行授权用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•吉林南山街</t>
+          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
     </row>
@@ -13300,22 +13300,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -13337,17 +13337,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13357,29 +13357,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -13401,17 +13401,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13421,29 +13421,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13453,29 +13453,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13485,29 +13485,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13517,29 +13517,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13549,29 +13549,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13581,29 +13581,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13613,29 +13613,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13645,29 +13645,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
@@ -13689,17 +13689,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13709,29 +13709,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13741,29 +13741,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13773,29 +13773,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -13817,17 +13817,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13837,29 +13837,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13869,29 +13869,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
         </is>
       </c>
     </row>
@@ -13913,17 +13913,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -13945,17 +13945,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13965,29 +13965,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13997,29 +13997,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14029,29 +14029,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14061,29 +14061,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14093,7 +14093,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -14105,17 +14105,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14125,29 +14125,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
         </is>
       </c>
     </row>
@@ -14169,17 +14169,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14189,29 +14189,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -14233,17 +14233,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14253,29 +14253,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14285,29 +14285,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
         </is>
       </c>
     </row>
@@ -14329,17 +14329,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14349,7 +14349,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
         </is>
       </c>
     </row>
@@ -14361,17 +14361,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14381,29 +14381,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
@@ -14425,17 +14425,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14445,29 +14445,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14477,29 +14477,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14509,29 +14509,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14541,29 +14541,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
@@ -14585,17 +14585,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14605,7 +14605,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14622,12 +14622,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
@@ -14649,17 +14649,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14713,17 +14713,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14745,17 +14745,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14777,17 +14777,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14804,22 +14804,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14836,22 +14836,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14873,17 +14873,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14905,17 +14905,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14932,22 +14932,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14969,17 +14969,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14996,22 +14996,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -15028,22 +15028,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -15060,22 +15060,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15092,22 +15092,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15129,17 +15129,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15156,22 +15156,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15193,17 +15193,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15225,17 +15225,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15262,12 +15262,12 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15284,22 +15284,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15316,22 +15316,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15353,17 +15353,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -11205,7 +11205,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•吉林南山街</t>
+          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
+          <t>鸿蒙智行授权用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
     </row>
@@ -13300,22 +13300,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13325,29 +13325,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13357,29 +13357,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13389,29 +13389,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13421,29 +13421,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13453,29 +13453,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
@@ -13497,17 +13497,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13517,29 +13517,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13549,29 +13549,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13581,29 +13581,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13613,29 +13613,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13645,29 +13645,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13677,29 +13677,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13709,29 +13709,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
@@ -13780,22 +13780,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13805,29 +13805,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13837,29 +13837,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -13881,17 +13881,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13901,29 +13901,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13933,29 +13933,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
@@ -14009,17 +14009,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14029,29 +14029,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14061,29 +14061,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14093,7 +14093,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
@@ -14105,17 +14105,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14125,29 +14125,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -14169,17 +14169,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14189,29 +14189,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
@@ -14260,22 +14260,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14285,29 +14285,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -14329,17 +14329,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14349,29 +14349,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
@@ -14393,17 +14393,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14413,29 +14413,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14445,29 +14445,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14477,29 +14477,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14509,29 +14509,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14541,29 +14541,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
@@ -14745,17 +14745,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14772,22 +14772,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14809,17 +14809,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14836,22 +14836,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14868,22 +14868,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14905,17 +14905,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14932,22 +14932,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14969,17 +14969,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14996,22 +14996,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -15028,22 +15028,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -15060,22 +15060,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15092,22 +15092,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15129,17 +15129,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15161,17 +15161,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15188,22 +15188,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15220,22 +15220,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15257,17 +15257,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15284,22 +15284,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15316,22 +15316,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15353,17 +15353,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15385,17 +15385,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（55家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（59家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（54家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（58家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -662,17 +662,17 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>848</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
     </row>
@@ -782,23 +782,23 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="2" t="n">
         <v>535</v>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>534</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
+      <c r="C15" s="2" t="n">
+        <v>535</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8721</v>
+        <v>8722</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8717</v>
+        <v>8718</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-4</v>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E183" s="2" t="n">
         <v>0</v>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
@@ -4785,14 +4785,14 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>0</v>
@@ -4806,14 +4806,14 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>0</v>
@@ -4827,14 +4827,14 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="E187" s="2" t="n">
         <v>0</v>
@@ -4848,14 +4848,14 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E188" s="2" t="n">
         <v>0</v>
@@ -4869,14 +4869,14 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E190" s="2" t="n">
         <v>0</v>
@@ -4911,14 +4911,14 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E191" s="2" t="n">
         <v>0</v>
@@ -4932,14 +4932,14 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>0</v>
@@ -4953,14 +4953,14 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E193" s="2" t="n">
         <v>0</v>
@@ -4974,38 +4974,38 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C194" s="2" t="n">
+      <c r="C195" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D194" s="2" t="n">
+      <c r="D195" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E194" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="3" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C195" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="D195" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E195" s="3" t="n">
-        <v>1</v>
+      <c r="E195" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -5016,14 +5016,14 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C196" s="3" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="E196" s="3" t="n">
         <v>1</v>
@@ -7956,38 +7956,38 @@
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C336" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D336" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E336" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="4" t="inlineStr">
+      <c r="A337" s="2" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B337" s="4" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C337" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D337" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="E337" s="4" t="n">
-        <v>-1</v>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D337" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E337" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C338" s="2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E338" s="2" t="n">
         <v>0</v>
@@ -8019,14 +8019,14 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C339" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E339" s="2" t="n">
         <v>0</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E341" s="2" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D343" s="2" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E343" s="2" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0</v>
@@ -10080,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10088,6 +10088,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10116,6 +10117,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -10143,6 +10149,11 @@
           <t>大同经济技术开发区湖滨大街31号汽车展厅A店</t>
         </is>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -10170,6 +10181,11 @@
           <t>湖北省武汉市汉阳区江城大道369号</t>
         </is>
       </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -10197,6 +10213,11 @@
           <t>山东省东营市东营区北一路730号西城万达商场1楼西圆厅</t>
         </is>
       </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -10206,22 +10227,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏太百购物中心</t>
+          <t>小米汽车江苏苏州张家港张家港曼巴特广场</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>阿克苏地区</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区阿克苏地区阿克苏市新华东路33-1号</t>
+          <t>江苏省苏州市张家港市杨舍镇河西路88号曼巴特购物中心一楼中庭</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10233,22 +10259,27 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>小米汽车江苏苏州张家港张家港曼巴特广场</t>
+          <t>小米汽车浙江省绍兴市越城区苏宁广场</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>绍兴市</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇河西路88号曼巴特购物中心一楼中庭</t>
+          <t>灵芝街道解放大道190号</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10260,49 +10291,59 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴市越城区苏宁广场</t>
+          <t>小米汽车福建漳州市龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>绍兴市</t>
+          <t>漳州市</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>灵芝街道解放大道190号</t>
+          <t>福建省漳州市龙文区建元东路2号‌</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州市龙文区碧湖万达</t>
+          <t>小鹏汽车北京亦庄交付中心</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>漳州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区建元东路2号‌</t>
+          <t>北京市经济技术开发区科创三街15号A1幢</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260511~20260511，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10314,22 +10355,27 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄交付中心</t>
+          <t>小鹏汽车芜湖华强吾悦广场销售展厅</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢</t>
+          <t>安徽省芜湖市镜湖区长江中路77号华强吾悦广场1020-1、1020-2铺位</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10341,22 +10387,27 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车芜湖华强吾悦广场销售展厅</t>
+          <t>小鹏汽车深圳龙岗百世汽车城销售服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>安徽省芜湖市镜湖区长江中路77号华强吾悦广场1020-1、1020-2铺位</t>
+          <t>深圳市龙岗区宝龙街道南约社区植物园路144号翠华达南约工业厂区5号厂房101</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10368,22 +10419,27 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗百世汽车城销售服务中心</t>
+          <t>小鹏汽车扬州高邮销售展厅</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>扬州市</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区宝龙街道南约社区植物园路144号翠华达南约工业厂区5号厂房101</t>
+          <t>高邮市中心大道129-10</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10395,22 +10451,27 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州高邮销售展厅</t>
+          <t>小鹏汽车衡水西环路服务中心</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>扬州市</t>
+          <t>衡水市</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>高邮市中心大道129-10</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10422,22 +10483,27 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水西环路服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>衡水市</t>
+          <t>周口市</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10449,22 +10515,27 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>周口市</t>
+          <t>长沙市</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>湖南省长沙市浏阳市集里街道S207</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10476,49 +10547,59 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>长沙市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>湖南省长沙市浏阳市集里街道S207</t>
+          <t>重庆市沙坪坝区西林大道84号融创茂</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>上海世博源新能源空间</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>重庆市沙坪坝区西林大道84号融创茂</t>
+          <t>上海市浦东新区上南路168号世博源4区</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10530,22 +10611,27 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>上海世博源新能源空间</t>
+          <t>广元万达广场新能源空间</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广元市</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>上海市浦东新区上南路168号世博源4区</t>
+          <t>四川省广元市利州区万缘街道万源万达广场1楼中庭</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10557,22 +10643,27 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>广元万达广场新能源空间</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>广元市</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>四川省广元市利州区万缘街道万源万达广场1楼中庭</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10584,22 +10675,27 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>常州飞龙吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>广州市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>江苏省常州市新北区飞龙中路166号</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10707,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>常州飞龙吾悦广场新能源空间</t>
+          <t>扬州京华城新能源空间</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -10621,12 +10717,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>扬州市</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙中路166号</t>
+          <t>江苏省扬州市邗江区京华城路168号</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10638,22 +10739,27 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>扬州京华城新能源空间</t>
+          <t>赣州龙南万达新能源空间</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>扬州市</t>
+          <t>赣州市</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>江苏省扬州市邗江区京华城路168号</t>
+          <t>江西省赣州市龙南市龙南镇龙翔大道1号门</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10665,22 +10771,27 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>赣州龙南万达新能源空间</t>
+          <t>沈阳中街吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>赣州市</t>
+          <t>沈阳市</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>江西省赣州市龙南市龙南镇龙翔大道1号门</t>
+          <t>辽宁省沈阳市大东区津桥路7号沈阳中街</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10692,22 +10803,27 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>沈阳中街吾悦广场新能源空间</t>
+          <t>渭南临渭万达新能源空间</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>沈阳市</t>
+          <t>渭南市</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>辽宁省沈阳市大东区津桥路7号沈阳中街</t>
+          <t>陕西省渭南市临渭区渭河大街与仓程路十字西北角渭南临渭万达广场一层</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10719,49 +10835,59 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>渭南临渭万达新能源空间</t>
+          <t>大庆星耀天地新能源空间</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>渭南市</t>
+          <t>大庆市</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>陕西省渭南市临渭区渭河大街与仓程路十字西北角渭南临渭万达广场一层</t>
+          <t>黑龙江省大庆市龙凤区世纪大道与龙永路交叉口</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>大庆星耀天地新能源空间</t>
+          <t>上海万象城</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>大庆市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区世纪大道与龙永路交叉口</t>
+          <t>上海市闵行区吴中路1599号万象城西入口</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10773,22 +10899,27 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>上海万象城</t>
+          <t>合肥包河万象汇</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>合肥市</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>上海市闵行区吴中路1599号万象城西入口</t>
+          <t>安徽省合肥市包河区包河大道与龙川路交叉口东北角B1层CB123展位</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10800,22 +10931,27 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>合肥包河万象汇</t>
+          <t>深圳宝安航城特斯拉中心</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>合肥市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>安徽省合肥市包河区包河大道与龙川路交叉口东北角B1层CB123展位</t>
+          <t>广东省深圳市宝安区航城街道利锦社区锦昌一路3号（睿盛商业楼）</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10827,22 +10963,27 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳宝安航城特斯拉中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>扬州市</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区航城街道利锦社区锦昌一路3号（睿盛商业楼）</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10995,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>无锡万象城体验店</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -10864,12 +11005,17 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>扬州市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>江苏省无锡市滨湖区金石路188号万象城西区L110</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10881,7 +11027,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>无锡万象城体验店</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -10891,12 +11037,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>江苏省无锡市滨湖区金石路188号万象城西区L110</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10926,6 +11077,11 @@
           <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -10935,49 +11091,59 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>重庆中央公园光环花园城</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>重庆市两江新区同茂大道236号B-L1-18铺位</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>重庆中央公园光环花园城</t>
+          <t>理想汽车四平铁东零售展厅</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四平市</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>重庆市两江新区同茂大道236号B-L1-18铺位</t>
+          <t>吉林省四平市开发区大路4189号</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10989,22 +11155,27 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>理想汽车四平铁东零售展厅</t>
+          <t>理想汽车青岛重庆南路零售展厅</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>四平市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>吉林省四平市开发区大路4189号</t>
+          <t>山东省青岛市市北区重庆南路与长沙路交汇处</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11016,22 +11187,27 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>理想汽车青岛重庆南路零售展厅</t>
+          <t>理想汽车河源源城零售中心</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>河源市</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区重庆南路与长沙路交汇处</t>
+          <t>广东省河源市源城区河埔大道南260号理想汽车零售中心</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11043,22 +11219,27 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>理想汽车河源源城零售中心</t>
+          <t>理想汽车南京景枫中心零售中心</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>河源市</t>
+          <t>南京市</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>广东省河源市源城区河埔大道南260号理想汽车零售中心</t>
+          <t>江苏省南京市江宁区双龙大道1698号景枫中心一楼F125-9号商铺</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11070,22 +11251,27 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>理想汽车南京景枫中心零售中心</t>
+          <t>理想汽车佳木斯万达零售展厅</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>南京市</t>
+          <t>佳木斯市</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>江苏省南京市江宁区双龙大道1698号景枫中心一楼F125-9号商铺</t>
+          <t>黑龙江省佳木斯市向阳区光复西路1081号</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11097,7 +11283,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>理想汽车佳木斯万达零售展厅</t>
+          <t>理想汽车牡丹江万达广场零售展厅</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -11107,66 +11293,81 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>佳木斯市</t>
+          <t>牡丹江市</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>黑龙江省佳木斯市向阳区光复西路1081号</t>
+          <t>黑龙江省牡丹江市西安区西新安街358号1021店铺</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>理想汽车牡丹江万达广场零售展厅</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>牡丹江市</t>
+          <t>龙岩市</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>黑龙江省牡丹江市西安区西新安街358号1021店铺</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>龙岩市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11178,22 +11379,27 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>吉林市</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+          <t>吉林市高新区南山街2488号</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11411,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
+          <t>鸿蒙智行授权用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11221,6 +11427,11 @@
       <c r="E42" s="3" t="inlineStr">
         <is>
           <t>吉林市高新区南山街2488号</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11232,22 +11443,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•吉林南山街</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>吉林市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>吉林市高新区南山街2488号</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11259,22 +11475,27 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>临沂市</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+          <t>山东省临沂市兰山区孝河路80号万达广场一楼1010B/1012</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11507,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（万达广场）</t>
+          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -11296,12 +11517,17 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>临沂市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>山东省临沂市兰山区孝河路80号万达广场一楼1010B/1012</t>
+          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11313,7 +11539,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -11323,12 +11549,17 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11340,22 +11571,27 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•广州新塘永旺梦乐城</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>广东省广州市增城区新塘永旺1楼华为智能生活馆（西町村屋对面）</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11603,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•广州新塘永旺梦乐城</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -11377,12 +11613,17 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>广州市</t>
+          <t>肇庆市</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市增城区新塘永旺1楼华为智能生活馆（西町村屋对面）</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11394,22 +11635,27 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>华为授权体验店（桥北印象汇）</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>肇庆市</t>
+          <t>南京市</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
+          <t>江苏省南京市浦口区大桥北街58号印象汇第一层第01-19/20号</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11667,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥北印象汇）</t>
+          <t>AITO授权用户中心•南通青年中路</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -11431,12 +11677,17 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>南京市</t>
+          <t>南通市</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区大桥北街58号印象汇第一层第01-19/20号</t>
+          <t>江苏省南通市崇川区观音山街道青年中路157号</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11448,22 +11699,27 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南通青年中路</t>
+          <t>鸿蒙智行授权用户中心•武汉张家湾东富汽车园</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>南通市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区观音山街道青年中路157号</t>
+          <t>武汉市洪山区张家湾街烽火路特2号张家湾国际汽车科技园（一汽大众）</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11475,22 +11731,27 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•武汉张家湾东富汽车园</t>
+          <t>鸿蒙智行授权用户中心•常德龙港路</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>武汉市</t>
+          <t>常德市</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>武汉市洪山区张家湾街烽火路特2号张家湾国际汽车科技园（一汽大众）</t>
+          <t>湖南省常德市武陵区南坪街道龙港路999号</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11763,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•常德龙港路</t>
+          <t>鸿蒙智行尚界用户中心•湘潭九华汽车城</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -11512,12 +11773,17 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>常德市</t>
+          <t>湘潭市</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区南坪街道龙港路999号</t>
+          <t>湖南省湘潭市雨湖区湘望路5号</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11529,22 +11795,27 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•湘潭九华汽车城</t>
+          <t>AITO授权用户中心•兰州安宁国际汽车城</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>湘潭市</t>
+          <t>兰州市</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>湖南省湘潭市雨湖区湘望路5号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1749附1号第一层001室-2号（安宁汽车城）</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11556,49 +11827,27 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•兰州安宁国际汽车城</t>
+          <t>鸿蒙智行授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>兰州市</t>
+          <t>六盘水市</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1749附1号第一层001室-2号（安宁汽车城）</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•六盘水钟山</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>六盘水市</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
           <t>贵州省六盘水市钟山区钟山西路白鹤高架桥北侧汽车文化广场（临时营业）</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11613,7 +11862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11621,6 +11870,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11649,6 +11899,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -11676,6 +11931,11 @@
           <t>北京市大兴区金时大街7号院10号楼</t>
         </is>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -11703,6 +11963,11 @@
           <t>广东省湛江市赤坎区东盛路7号</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -11730,6 +11995,11 @@
           <t>江苏省南通市崇川区星湖大道1085号</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -11757,6 +12027,11 @@
           <t>湖南省长沙市岳麓区长沙高新开发区嘉运路36号</t>
         </is>
       </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -11784,6 +12059,11 @@
           <t>陕西省西安市长安区常宁大街369号</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -11811,6 +12091,11 @@
           <t>黑龙江省大庆市龙凤区庆新大街17号</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -11838,6 +12123,11 @@
           <t>延吉万达</t>
         </is>
       </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -11865,6 +12155,11 @@
           <t>安徽省合肥市庐阳区庐阳万象汇1F1号门入口</t>
         </is>
       </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -11892,6 +12187,11 @@
           <t>广东省梅州市梅县区剑英大道南（锦绣国际家居建材城旁）</t>
         </is>
       </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -11919,6 +12219,11 @@
           <t>上高路186号</t>
         </is>
       </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 1 期</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -11946,6 +12251,11 @@
           <t>江苏省镇江市润州区官塘桥路299号</t>
         </is>
       </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -11973,6 +12283,11 @@
           <t>浙江省湖州市安吉县昌硕街道云鸿东路1号 安吉浙北购物中心</t>
         </is>
       </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -12000,6 +12315,11 @@
           <t>鸭绿江街32甲号</t>
         </is>
       </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -12027,6 +12347,11 @@
           <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -12054,6 +12379,11 @@
           <t>上海虹口区东大名路999号北外滩来福士【01-01/01】铺</t>
         </is>
       </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -12081,6 +12411,11 @@
           <t>北京市石景山区阜石路173号院1号楼京西大悦城1F-09</t>
         </is>
       </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -12108,6 +12443,11 @@
           <t>深圳市龙岗区吉祥路555号</t>
         </is>
       </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -12135,6 +12475,11 @@
           <t>乌鲁木齐市米东区府前西路600号米东吾悦广场一楼1062号</t>
         </is>
       </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -12162,6 +12507,11 @@
           <t>福建省南平市建阳区大红袍路2号南平万达广场-1B层1B002A</t>
         </is>
       </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -12189,6 +12539,11 @@
           <t>河北省保定市莲池区七一东路2456号中冀汽车集团院内</t>
         </is>
       </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -12216,6 +12571,11 @@
           <t>山东省济南市历下区泉城路188号西翼一层162号店铺</t>
         </is>
       </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -12243,6 +12603,11 @@
           <t>福建省厦门市思明区梧村街道湖滨东路99号厦门万象城B2层中庭</t>
         </is>
       </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -12270,6 +12635,11 @@
           <t>上海市浦东新区张杨路2757号1幢106室</t>
         </is>
       </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -12297,6 +12667,11 @@
           <t>北京市朝阳区-金港大道1号金港汽车公园5号楼1层1号</t>
         </is>
       </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -12324,6 +12699,11 @@
           <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -12351,6 +12731,11 @@
           <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -12378,6 +12763,11 @@
           <t>四川省绵阳市涪城区花园路9号万达广场【1F】层【1052A，1052B】号商铺</t>
         </is>
       </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -12405,6 +12795,11 @@
           <t>安徽省合肥市政务区潜山路 111 号合肥万象城理想汽车</t>
         </is>
       </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -12432,6 +12827,11 @@
           <t>安徽省安庆市宜秀区安庆市石塘湖路10号东风日产安庆恒业专卖店</t>
         </is>
       </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -12459,6 +12859,11 @@
           <t>兰山区沂蒙路159号</t>
         </is>
       </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -12486,6 +12891,11 @@
           <t>山东省日照市东港区烟台路176号华润万象汇L1193号商铺</t>
         </is>
       </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -12513,6 +12923,11 @@
           <t>云浮市环市东路牧羊朱屋村与罗沙稔塘村交界处</t>
         </is>
       </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -12540,6 +12955,11 @@
           <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -12567,6 +12987,11 @@
           <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -12594,6 +13019,11 @@
           <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -12621,6 +13051,11 @@
           <t>江苏省南京市溧水区溧星路10号理想汽车</t>
         </is>
       </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -12648,6 +13083,11 @@
           <t>江苏省常州市钟楼区延陵西路123号吾悦广场一楼6-101-1</t>
         </is>
       </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -12675,6 +13115,11 @@
           <t>江苏省徐州市玉带大道6号杉杉奥特莱斯广场理想汽车</t>
         </is>
       </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -12702,6 +13147,11 @@
           <t>江苏省苏州市常熟市东南大道158号永旺梦乐城1F124-1号铺位1楼北三门理想汽车</t>
         </is>
       </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -12729,6 +13179,11 @@
           <t>江西省宜春经济技术开发区春顺路北200米</t>
         </is>
       </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -12756,6 +13211,11 @@
           <t xml:space="preserve">浙江省杭州市下城区石祥东路1726号3号楼108室   </t>
         </is>
       </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -12765,49 +13225,59 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 合肥万象城</t>
+          <t>蔚来空间 | 武汉金银潭永旺</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>合肥市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>安徽省合肥市蜀山区潜山路111号合肥万象城L127号</t>
+          <t>湖北省武汉市东西湖区将军路街道金银潭大道1号永旺梦乐城第一层165b-1</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉金银潭永旺</t>
+          <t>华为授权体验店（宜家荟聚）</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>武汉市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>湖北省武汉市东西湖区将军路街道金银潭大道1号永旺梦乐城第一层165b-1</t>
+          <t>上海市长宁区金钟路788号01C04A 华为</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12819,22 +13289,27 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（宜家荟聚）</t>
+          <t>AITO授权用户中心•北京欢乐谷</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>上海市长宁区金钟路788号01C04A 华为</t>
+          <t>北京市朝阳区东四环南路56号D座1层</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12846,22 +13321,27 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•北京欢乐谷</t>
+          <t>AITO授权用户中心•天津西青大寺汽车园</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区东四环南路56号D座1层</t>
+          <t>天津市西青区大寺镇储源道17号</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12873,22 +13353,27 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•天津西青大寺汽车园</t>
+          <t>华为智能生活馆•烟台芝罘万达</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>烟台市</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>天津市西青区大寺镇储源道17号</t>
+          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12900,22 +13385,27 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台芝罘万达</t>
+          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>烟台市</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
+          <t>广东省广州市天河区广汕一路6号103房</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12927,7 +13417,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•广州天河广汕路</t>
+          <t>华为智能生活馆•惠州华贸天地</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -12937,12 +13427,17 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>广州市</t>
+          <t>惠州市</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市天河区广汕一路6号103房</t>
+          <t>广东省惠州市惠城区江北文昌一路九号惠州华贸天地L1-1101D商铺华为智能生活馆•惠州华贸天地</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12954,22 +13449,27 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•惠州华贸天地</t>
+          <t>鸿蒙智行享界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>惠州市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>广东省惠州市惠城区江北文昌一路九号惠州华贸天地L1-1101D商铺华为智能生活馆•惠州华贸天地</t>
+          <t>中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 1 期</t>
         </is>
       </c>
     </row>
@@ -12981,22 +13481,27 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•南宁五象钜荣汽车园</t>
+          <t>华为智能生活馆•无锡八佰伴中心</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13008,22 +13513,27 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•无锡八佰伴中心</t>
+          <t>鸿蒙智行授权用户中心•南昌新兴西大道</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>南昌市</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
+          <t>江西省南昌市红谷滩区新兴西大道69号</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13035,7 +13545,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南昌新兴西大道</t>
+          <t>AITO授权用户中心•吉安长丰大道</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -13045,12 +13555,17 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>南昌市</t>
+          <t>吉安市</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区新兴西大道69号</t>
+          <t>江西省吉安市吉州区长塘镇长丰大道186号</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13062,22 +13577,27 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•吉安长丰大道</t>
+          <t>华为智能生活馆•嘉兴平湖吾悦</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>吉安市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>江西省吉安市吉州区长塘镇长丰大道186号</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13089,22 +13609,27 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴平湖吾悦</t>
+          <t>AITO授权用户中心·楚天威汉</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
+          <t>湖北省武汉市</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13116,22 +13641,27 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·楚天威汉</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>武汉市</t>
+          <t>福州市</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>湖北省武汉市</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13673,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -13158,7 +13688,12 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13170,22 +13705,27 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>鸿蒙智行授权用户中心•遵义汇川</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13197,49 +13737,27 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遵义汇川</t>
+          <t>华为智能生活馆•宝鸡开元商城</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>宝鸡市</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•宝鸡开元商城</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>宝鸡市</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
           <t>陕西省宝鸡市渭滨区经二路154号宝鸡开元商城1F-C-08号</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13300,22 +13818,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13325,29 +13843,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13357,29 +13875,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13389,29 +13907,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13421,29 +13939,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13453,29 +13971,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13485,29 +14003,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13517,29 +14035,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13549,29 +14067,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13581,29 +14099,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13613,29 +14131,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13645,29 +14163,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13677,29 +14195,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13709,29 +14227,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13741,29 +14259,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13773,7 +14291,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
@@ -13785,17 +14303,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13805,29 +14323,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13837,7 +14355,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -13849,17 +14367,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13869,7 +14387,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -13881,17 +14399,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13901,29 +14419,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13933,29 +14451,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13965,7 +14483,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
@@ -13977,17 +14495,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13997,29 +14515,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14029,7 +14547,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
@@ -14041,17 +14559,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14061,29 +14579,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14093,7 +14611,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
         </is>
       </c>
     </row>
@@ -14105,17 +14623,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14125,29 +14643,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14157,7 +14675,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
         </is>
       </c>
     </row>
@@ -14169,17 +14687,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14189,29 +14707,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14221,29 +14739,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14253,7 +14771,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
@@ -14270,12 +14788,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14285,29 +14803,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14317,7 +14835,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
         </is>
       </c>
     </row>
@@ -14329,17 +14847,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14349,29 +14867,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14381,7 +14899,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -14398,12 +14916,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14413,29 +14931,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14445,7 +14963,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
@@ -14457,17 +14975,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14477,29 +14995,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14509,29 +15027,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14541,29 +15059,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>AITO授权用户中心•海口琼山大道</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14573,29 +15091,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14605,7 +15123,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14649,17 +15167,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14669,29 +15187,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14701,7 +15219,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14713,17 +15231,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14745,17 +15263,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14772,22 +15290,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14809,17 +15327,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14836,22 +15354,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14868,22 +15386,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14900,22 +15418,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14937,17 +15455,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14969,17 +15487,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -15001,17 +15519,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -15028,22 +15546,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -15060,22 +15578,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15092,22 +15610,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15129,17 +15647,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15161,17 +15679,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15188,22 +15706,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15252,22 +15770,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15289,17 +15807,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15321,17 +15839,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15353,17 +15871,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15385,17 +15903,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -11027,7 +11027,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -11870,7 +11870,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车北京朝阳授权服务中心（金驰之星店）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12765,7 +12765,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车揭阳榕城万达零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12937,7 +12937,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12984,12 +12984,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13001,7 +13001,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -13016,12 +13016,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车沧州吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13469,7 +13469,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>连续在档 1 期</t>
+          <t>连续在档 1 期；本期存在高相似店名「鸿蒙智行智界用户中心•南宁五象钜荣汽车园」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -13673,7 +13673,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -13688,7 +13688,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -13818,22 +13818,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13939,14 +13939,14 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -13956,12 +13956,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13971,14 +13971,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -14163,29 +14163,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -14195,29 +14195,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
         </is>
       </c>
     </row>
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -14259,29 +14259,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>华为智能生活馆•深圳龙华壹方城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
         </is>
       </c>
     </row>
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14355,29 +14355,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14387,29 +14387,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14419,29 +14419,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>鸿蒙智行授权用户中心•上海北松公路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14451,29 +14451,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14515,29 +14515,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14611,29 +14611,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>AITO授权用户中心•西安航天</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
         </is>
       </c>
     </row>
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>AITO授权用户中心•石家庄长安汽车园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14675,29 +14675,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14707,29 +14707,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14739,29 +14739,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>AITO授权用户中心•大庆高新汽车工业园</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14835,29 +14835,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14899,29 +14899,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14931,29 +14931,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14963,29 +14963,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>AITO授权用户中心•南昌高新大道</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14995,29 +14995,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>AITO授权用户中心•通化新胜北路</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -15027,29 +15027,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -15098,22 +15098,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -15123,29 +15123,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -15155,7 +15155,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -15172,12 +15172,12 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15354,22 +15354,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15386,22 +15386,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -15418,22 +15418,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -15578,22 +15578,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15610,22 +15610,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -15642,22 +15642,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15706,22 +15706,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15738,22 +15738,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15770,22 +15770,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15834,22 +15834,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15871,17 +15871,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15898,22 +15898,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（54家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（58家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（67条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（56家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（51条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,23 +845,23 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
-        <v>1717</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>1717</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="B18" s="4" t="n">
+        <v>1458</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1451</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8722</v>
+        <v>8463</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8718</v>
+        <v>8452</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
     </row>
@@ -9426,14 +9426,14 @@
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C406" s="4" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D406" s="4" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E406" s="4" t="n">
         <v>-2</v>
@@ -9447,17 +9447,17 @@
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C407" s="4" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D407" s="4" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E407" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="408">
@@ -9468,14 +9468,14 @@
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C408" s="4" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="D408" s="4" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="E408" s="4" t="n">
         <v>-1</v>
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C409" s="4" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="D409" s="4" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="E409" s="4" t="n">
         <v>-1</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C410" s="4" t="n">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="D410" s="4" t="n">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="E410" s="4" t="n">
         <v>-1</v>
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="4" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C411" s="4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D411" s="4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E411" s="4" t="n">
         <v>-1</v>
@@ -9556,10 +9556,10 @@
         </is>
       </c>
       <c r="C412" s="4" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D412" s="4" t="n">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E412" s="4" t="n">
         <v>-1</v>
@@ -9573,59 +9573,59 @@
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C413" s="4" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D413" s="4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E413" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="inlineStr">
+      <c r="A414" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B414" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C414" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D414" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="E414" s="2" t="n">
-        <v>0</v>
+      <c r="B414" s="4" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="C414" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D414" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="E414" s="4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B415" s="2" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C415" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="D415" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="E415" s="2" t="n">
-        <v>0</v>
+      <c r="B415" s="4" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C415" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="416">
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D416" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D417" s="2" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D420" s="2" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E420" s="2" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D424" s="2" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D425" s="2" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D426" s="2" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="E426" s="2" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D427" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E427" s="2" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D428" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E428" s="2" t="n">
         <v>0</v>
@@ -9909,80 +9909,80 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D429" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E429" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D430" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E430" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D431" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E431" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C429" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="D429" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E429" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B430" s="3" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C430" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="D430" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="E430" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B431" s="3" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C431" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="D431" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="E431" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B432" s="3" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C432" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="D432" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="E432" s="3" t="n">
-        <v>1</v>
+      <c r="C432" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D432" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E432" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="433">
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C433" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D433" s="3" t="n">
         <v>19</v>
-      </c>
-      <c r="D433" s="3" t="n">
-        <v>20</v>
       </c>
       <c r="E433" s="3" t="n">
         <v>1</v>
@@ -10014,17 +10014,17 @@
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C434" s="3" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D434" s="3" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="E434" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="B435" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C435" s="3" t="n">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D435" s="3" t="n">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="E435" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
@@ -10056,17 +10056,17 @@
       </c>
       <c r="B436" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C436" s="3" t="n">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D436" s="3" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E436" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10080,13 +10080,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
@@ -11347,27 +11347,27 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>鸿蒙智行授权用户中心•吉林南山街</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>吉林市</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+          <t>吉林市高新区南山街2488号</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11379,27 +11379,27 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•吉林南山街</t>
+          <t>华为授权体验店（万达广场）</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>吉林市</t>
+          <t>临沂市</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>吉林市高新区南山街2488号</t>
+          <t>山东省临沂市兰山区孝河路80号万达广场一楼1010B/1012</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11411,27 +11411,27 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•吉林南山街</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>吉林市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>吉林市高新区南山街2488号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11443,27 +11443,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>华为智能生活馆•广州新塘永旺梦乐城</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+          <t>广东省广州市增城区新塘永旺1楼华为智能生活馆（西町村屋对面）</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11475,27 +11475,27 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（万达广场）</t>
+          <t>华为授权体验店（桥北印象汇）</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>临沂市</t>
+          <t>南京市</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>山东省临沂市兰山区孝河路80号万达广场一楼1010B/1012</t>
+          <t>江苏省南京市浦口区大桥北街58号印象汇第一层第01-19/20号</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11507,27 +11507,27 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
+          <t>AITO授权用户中心•南通青年中路</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>南通市</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+          <t>江苏省南通市崇川区观音山街道青年中路157号</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11539,315 +11539,27 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>AITO授权用户中心•兰州安宁国际汽车城</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>兰州市</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1749附1号第一层001室-2号（安宁汽车城）</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•广州新塘永旺梦乐城</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>广东省广州市增城区新塘永旺1楼华为智能生活馆（西町村屋对面）</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
           <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>肇庆市</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>华为授权体验店（桥北印象汇）</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>南京市</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>江苏省南京市浦口区大桥北街58号印象汇第一层第01-19/20号</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•南通青年中路</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>南通市</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>江苏省南通市崇川区观音山街道青年中路157号</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•武汉张家湾东富汽车园</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>武汉市</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>武汉市洪山区张家湾街烽火路特2号张家湾国际汽车科技园（一汽大众）</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•常德龙港路</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>常德市</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>湖南省常德市武陵区南坪街道龙港路999号</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•湘潭九华汽车城</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>湘潭市</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>湖南省湘潭市雨湖区湘望路5号</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•兰州安宁国际汽车城</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>兰州市</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1749附1号第一层001室-2号（安宁汽车城）</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•六盘水钟山</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>六盘水市</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>贵州省六盘水市钟山区钟山西路白鹤高架桥北侧汽车文化广场（临时营业）</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12969,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12984,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13001,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -13016,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13449,27 +13161,27 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•南宁五象钜荣汽车园</t>
+          <t>华为智能生活馆•无锡八佰伴中心</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>连续在档 1 期；本期存在高相似店名「鸿蒙智行智界用户中心•南宁五象钜荣汽车园」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13481,22 +13193,22 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•无锡八佰伴中心</t>
+          <t>AITO授权用户中心•吉安长丰大道</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>吉安市</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
+          <t>江西省吉安市吉州区长塘镇长丰大道186号</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -13513,27 +13225,27 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南昌新兴西大道</t>
+          <t>华为智能生活馆•嘉兴平湖吾悦</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>南昌市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区新兴西大道69号</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13545,22 +13257,22 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•吉安长丰大道</t>
+          <t>AITO授权用户中心·楚天威汉</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>吉安市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>江西省吉安市吉州区长塘镇长丰大道186号</t>
+          <t>湖北省武汉市</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -13577,22 +13289,22 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴平湖吾悦</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
+          <t>福州市</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -13609,22 +13321,22 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·楚天威汉</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>武汉市</t>
+          <t>福州市</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>湖北省武汉市</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -13641,22 +13353,22 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>鸿蒙智行授权用户中心•遵义汇川</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -13673,89 +13385,25 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•宝鸡开元商城</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>福州市</t>
+          <t>宝鸡市</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>陕西省宝鸡市渭滨区经二路154号宝鸡开元商城1F-C-08号</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 7 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•遵义汇川</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>遵义市</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 7 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•宝鸡开元商城</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>宝鸡市</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>陕西省宝鸡市渭滨区经二路154号宝鸡开元商城1F-C-08号</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>连续在档 7 期</t>
         </is>
@@ -13772,7 +13420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13818,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13843,29 +13491,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13875,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13907,7 +13555,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -13919,17 +13567,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13939,29 +13587,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13971,7 +13619,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13983,17 +13631,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -14003,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14035,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•榆林东沙汽车产业园</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -14067,29 +13715,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区汽车产业园产业三路D1-01-02 → 陕西省榆林市榆阳区汽车产业园产业三路D1-01-01</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -14099,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•茂名开发区汽车城</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -14131,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区茂南大道北侧站南直三街西侧001房屋 → 广东省茂名市茂南大道南香路段南香村委北侧2号楼首层</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -14163,29 +13811,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -14195,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•延吉开发区汽车产业园</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -14227,7 +13875,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>吉林省延边朝鲜族自治州延吉市长白山东路4765号 → 吉林省延边朝鲜族自治州延吉市长白山东路4539号</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -14239,17 +13887,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -14259,29 +13907,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•深圳龙华壹方城</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -14291,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区龙华街道壹方天地C区L1层2号门外广场展厅 → 广东省深圳市龙华区龙华街道壹方天地C区L1层L1-051/051A号商铺</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -14323,7 +13971,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -14362,22 +14010,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•曲靖学府路</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14387,7 +14035,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>云南省曲靖市麒麟区学府路172号 → 云南省曲靖市经开区学府路172号</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14047,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14419,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海北松公路</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14451,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>上海市松江区北松公路6280号-5幢 → 上海市松江区北松公路6280号</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14483,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14515,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
@@ -14532,12 +14180,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14547,29 +14195,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14579,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14611,157 +14259,157 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号 → 重庆市渝北区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安航天</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市长安区航天基地东长安街399号 → 陕西省西安市长安区东长安街神州三路399号</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•石家庄长安汽车园</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市长安区太行北大街55号石家庄长安汽车园D区6号 → 河北省石家庄市长安区太行北大街55号石家长安汽车园区D区6号</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14771,7 +14419,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -14783,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14803,29 +14451,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>浙江省慈溪市横河镇前应路1176号 → 慈溪市横河镇前应路1176号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•大庆高新汽车工业园</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14835,29 +14483,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区开发区新兴西街2-1号 → 黑龙省大庆市高新区产业一区(新兴西街4号)</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14867,7 +14515,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -14879,17 +14527,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14899,7 +14547,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -14911,17 +14559,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14931,29 +14579,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14963,29 +14611,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南昌高新大道</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14995,29 +14643,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青山湖区高新大道708号C座 → 江西省南昌市青山湖区高新大道708号C院</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•通化新胜北路</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -15027,7 +14675,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>吉林省通化市开发区新胜北路2459号（北京现代5S店院内） → 吉林省通化市开发区新胜北路2459号（北京现代4S店院内）</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -15039,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -15059,29 +14707,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海口琼山大道</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -15091,71 +14739,71 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区琼山大道289-9号 → 海南省海口市美兰区琼山大道289-9号AITO授权用户中心</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -15167,27 +14815,27 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -15204,22 +14852,22 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -15231,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -15263,17 +14911,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -15290,22 +14938,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -15327,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15359,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15386,22 +15034,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -15423,537 +15071,25 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车抚州临川服务中心（王安石大道临时店）</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车抚州临川服务中心（汤显祖大道临时店）</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>西藏</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>嘉兴海宁银泰体验店</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•海南电动</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•南网电动</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•广西电动</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•贵州电动</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>宁夏</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车广东中山大信新都汇</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>濮阳德宇4S中心</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>濮阳德宇维修中心</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车抚州临川服务中心（王安石大道临时店）</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车抚州临川服务中心（汤显祖大道临时店）</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>店名相似度 100%</t>
         </is>

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>-7</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8463</v>
+        <v>8462</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8452</v>
+        <v>8451</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-11</v>
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D428" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E428" s="2" t="n">
         <v>0</v>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,14 +13747,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -13764,12 +13764,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,29 +14195,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -14276,12 +14276,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,29 +14291,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,29 +14323,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14426,22 +14426,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14490,22 +14490,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14522,22 +14522,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14586,22 +14586,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14650,22 +14650,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14746,22 +14746,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14874,22 +14874,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14938,22 +14938,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（56家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（51条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（56家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（51条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13471,17 +13471,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,14 +13747,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -13764,12 +13764,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -13818,22 +13818,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,29 +14195,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -14298,22 +14298,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
@@ -14362,22 +14362,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14490,22 +14490,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14522,22 +14522,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14586,22 +14586,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14682,22 +14682,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14746,22 +14746,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14874,22 +14874,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -11027,7 +11027,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -13631,17 +13631,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -14202,22 +14202,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,29 +14259,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,29 +14355,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14490,7 +14490,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -14500,12 +14500,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14650,22 +14650,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14682,22 +14682,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14820,12 +14820,12 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14874,22 +14874,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14970,22 +14970,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15002,7 +15002,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -15012,12 +15012,12 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15034,22 +15034,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（56家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（51条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（56家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（51条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,14 +13555,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,14 +13907,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13924,12 +13924,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -14234,22 +14234,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,29 +14259,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,29 +14323,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14372,12 +14372,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14458,7 +14458,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -14468,12 +14468,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14522,22 +14522,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14586,22 +14586,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14650,22 +14650,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14682,22 +14682,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14874,22 +14874,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14970,22 +14970,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15002,22 +15002,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15034,22 +15034,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（56家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（51条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（56家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（51条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13471,17 +13471,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,14 +13619,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -13636,12 +13636,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -13690,22 +13690,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,29 +14195,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
@@ -14271,17 +14271,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,29 +14291,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,29 +14323,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14372,12 +14372,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14458,22 +14458,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14522,22 +14522,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14554,22 +14554,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14586,22 +14586,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14682,22 +14682,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14874,22 +14874,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13471,17 +13471,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,14 +13715,14 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -13732,12 +13732,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,29 +14163,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,29 +14195,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14490,22 +14490,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14522,22 +14522,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14554,22 +14554,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14618,22 +14618,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14874,22 +14874,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14938,22 +14938,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -11027,7 +11027,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13471,17 +13471,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -13535,17 +13535,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
@@ -13631,17 +13631,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
@@ -13759,17 +13759,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,14 +13843,14 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -13860,12 +13860,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,29 +14163,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,29 +14195,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,29 +14259,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,29 +14291,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
         </is>
       </c>
     </row>
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,29 +14387,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴华府八佰伴零售展厅 → 理想汽车嘉兴华府八佰伴零售中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14426,7 +14426,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -14436,12 +14436,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14458,22 +14458,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14490,22 +14490,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14522,22 +14522,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14554,22 +14554,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14618,22 +14618,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14842,22 +14842,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14874,22 +14874,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14938,22 +14938,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都龙湖滨江天街零售中心</t>
+          <t>理想汽车成都锦宸天街零售中心</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
+          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>理想汽车成都锦宸天街零售中心</t>
+          <t>理想汽车成都龙湖滨江天街零售中心</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市新都区大丰街道大天路699号龙湖成都锦宸天街A馆-1F-57</t>
+          <t>四川省成都市成华区成华大道杉板桥路266号龙湖·成都滨江天街A馆-1F-03</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车成都龙湖蜀新天街零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -13476,12 +13476,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
@@ -13631,17 +13631,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
@@ -13663,17 +13663,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
@@ -13695,17 +13695,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,29 +14163,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,29 +14195,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
@@ -14394,22 +14394,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14426,22 +14426,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14458,22 +14458,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>理想汽车银川建发阅彩城零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14554,22 +14554,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14650,22 +14650,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14778,22 +14778,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14842,22 +14842,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14874,22 +14874,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心（新址）</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车银川建发阅彩城零售中心</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15002,22 +15002,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260615_vs_20260622.xlsx
@@ -11027,7 +11027,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>苏州相城龙湖天街</t>
+          <t>苏州大悦城体验店L1-52</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
+          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>苏州大悦城体验店L1-52</t>
+          <t>苏州相城龙湖天街</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号苏州大悦城L1-52号</t>
+          <t>江苏省苏州市相城区相城大道1399号A-1F-CN-ZT-02</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
+          <t>理想汽车广州花都骏壹万邦零售中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
+          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州花都骏壹万邦零售中心</t>
+          <t>理想汽车广州增城万达零售展厅</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12696,12 +12696,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市花都区骏壹万邦广场1层1203、1203A商铺</t>
+          <t>广东省广州市增城区增城万达广场理想汽车</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车广州花都零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>理想汽车广州增城万达零售展厅</t>
+          <t>理想汽车广州番禺服务中心（番禺大道店）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省广州市增城区增城万达广场理想汽车</t>
+          <t>广东省广州市番禺区番禺大道北22号之三102房,202房​</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>连续在档 7 期；本期存在高相似店名「理想汽车泉州鲤城万达零售展厅」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 7 期</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -13466,22 +13466,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳宝安沙井服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
+          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>兰博基尼</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>兰博基尼苏州</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车葫芦岛龙港零售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
+          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州浙南科技城交付中心</t>
+          <t>理想汽车北京超极合生汇零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
+          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
+          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都万象城零售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>理想汽车成都万象城零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位 → 浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米</t>
+          <t>四川省成都市成华区万年场华润万象城二期C馆118号 → 四川省成都市成华区双庆路1号成都万象城A馆AL198号商铺</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
+          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13747,14 +13747,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -13764,12 +13764,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>兰博基尼苏州</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>7 Chengji Avenue,Suzhou New District,Suzhou 215000 → 江苏省苏州市高新区城际大道7号一幢一楼 215000</t>
+          <t>江苏省徐州市新沂市大桥西路114号 → 江苏省徐州新沂市经济开发区上海路56号吾悦广场1021号铺位</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车兰州安宁零售中心</t>
+          <t>小鹏汽车绵阳同立汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
+          <t>四川省绵阳市经开区绵州大道中段6号 → 四川省绵阳市经开区绵州大段中段6号</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
+          <t>小鹏汽车衡水昌明大街销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
+          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衡水昌明大街销售服务中心</t>
+          <t>理想汽车兰州安宁零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省衡水市高新区西外环与人民路交口西行20米路北 → 河北省衡水市高新区胜利路南侧，顺兴大街西侧衡水敬诚橡胶贸易有限公司院内</t>
+          <t>甘肃省兰州市安宁区北滨河路88号汽车城内保时捷中心东侧 → 甘肃省兰州市安宁区北滨河西路1735号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车昆明万象城零售中心</t>
+          <t>小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
+          <t>浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101 → 浙江省温州市龙湾区瑶溪街道南洋大道1965号互联网大厦B幢1层101小鹏汽车温州浙南科技城交付中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>蔚来体验中心 | 梅州梅县</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
+          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
         </is>
       </c>
     </row>
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号</t>
+          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
         </is>
       </c>
     </row>
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>重庆市两江新区康美街道嘉材路26号2楼 → 重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车深圳龙岗联创销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢 → 北京经济技术开发区双羊路15号</t>
+          <t>深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技1栋厂房A、B区A101A201 → 广东省深圳市龙岗区南湾街道下李朗社区布澜路21号联创科技园1栋厂房A、BA201</t>
         </is>
       </c>
     </row>
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车深圳宝安沙井服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>杨桥中路277号 → 福建省福州市鼓楼区杨桥中路277号</t>
+          <t>广东省深圳市宝安区沙井街道大王山社区沙井南环路381号A1栋102 → 广东省深圳市宝安区新桥街道沙企社区中心路14号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 梅州梅县</t>
+          <t>蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -14099,29 +14099,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>梅州市梅县区扶大高管会剑英大道雪佛兰(梅州)4S店右边第二间展厅 → 梅州市梅县区扶大高管会剑英大道北梅县汽车城内广汽丰田4S店</t>
+          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京超极合生汇零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14131,29 +14131,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>北京市昌平区北清路1号院1号楼超极合生汇LG58号 → 北京市昌平区北清路1号院1号楼超极合生汇（东区）M层K-01</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>理想汽车昆明万象城零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>东阳宝龙广场 → 广福东街1121号东阳宝龙广场1楼中庭</t>
+          <t>云南省昆明市官渡区环城南路 1 号华润拓东商务中心的昆明万象城L109号理想汽车 → 云南省昆明市官渡区环城南路1号华润拓东商务中心昆明万象城的B131</t>
         </is>
       </c>
     </row>
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车随州高新服务中心（鹿鹤大道临时店）</t>
+          <t>理想汽车葫芦岛龙港零售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14195,14 +14195,14 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>湖北省随州市高新区鹿鹤大道28号1-3层101号 → 湖北省随州市曾都区鹿鹤大道28号1-3层101号</t>
+          <t>辽宁省葫芦岛市龙港区文兴南路40-3号楼 → 葫芦岛市龙港区辽宁省葫芦岛市龙港区文兴南路40-3号楼</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14227,29 +14227,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000 → 新疆巴州库尔勒市梨香辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>新疆伊宁市巴彦岱城投汽车产业园 → 新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>蚌埠银泰百货</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -14259,29 +14259,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>安徽省蚌埠市蚌山区东海大道4000号银泰百货一层A1010 → 安徽省蚌埠市蚌山区东海大道4000号银泰百货一层中岛</t>
+          <t>北京市大兴区枣园路8号居然之家大兴店内一层东侧 → 北京市大兴区枣园路8号居然之家</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店</t>
+          <t>理想汽车南京仙林万达茂零售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14291,29 +14291,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
+          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅</t>
+          <t>深圳福田卓悦中心体验店</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
+          <t>深圳福田卓悦中心体验店 → 深圳福田卓悦中心</t>
         </is>
       </c>
     </row>
@@ -14372,12 +14372,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心</t>
+          <t>理想汽车南京江北虹悦城零售展厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售中心 → 理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售展厅 → 理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
     </row>
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
+          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖麒麟授权钣喷中心（中致远店）</t>
+          <t>理想汽车西昌机场路零售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车西昌零售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
+          <t>理想汽车上海张杨路零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
+          <t>理想汽车上海金桥零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌机场路零售展厅</t>
+          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西昌零售展厅</t>
+          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14554,22 +14554,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇4S中心</t>
+          <t>小米汽车广东中山大信新都汇</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>濮阳德宇维修中心</t>
+          <t>小米汽车广东省中山市小榄大信新都汇</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14586,22 +14586,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海张杨路零售中心</t>
+          <t>嘉兴海宁银泰体验店</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车上海金桥零售中心</t>
+          <t>嘉兴海宁银泰城体验店B1013-1</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
+          <t>理想汽车茂名茂南授权钣喷中心（金成店）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车郑州东站威佳汽车园零售中心</t>
+          <t>理想汽车茂名茂南授权服务中心（金成店）</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14650,22 +14650,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>理想汽车郑州圃田威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>理想汽车郑州东站威佳汽车园零售中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
+          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
+          <t>理想汽车宜宾叙州临时交付中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14714,7 +14714,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -14724,12 +14724,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰体验店</t>
+          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>嘉兴海宁银泰城体验店B1013-1</t>
+          <t>理想汽车杭州城西银泰城零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心（新址）</t>
+          <t>理想汽车沧州任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车泉州浦西万达零售中心</t>
+          <t>理想汽车任丘悦都汇零售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14778,22 +14778,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>理想汽车北京朝阳授权钣喷中心（金驰之星店）</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>理想汽车北京朝阳授权服务中心（金驰之星店）</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14810,22 +14810,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车沧州任丘悦都汇零售展厅</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车任丘悦都汇零售展厅</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权钣喷中心（嘉骏店）</t>
+          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车梅州梅县授权服务中心（嘉骏店）</t>
+          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心（新）</t>
+          <t>理想汽车汉中汉台服务中心（三星汽贸临时店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口万象城零售中心</t>
+          <t>理想汽车汉中汉台授权服务中心（汉中三星店）</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权钣喷中心（奥星越秀店）</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州经开授权服务中心（奥星越秀店）</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州授权钣喷中心（宜捷路店）</t>
+          <t>理想汽车拉萨市城关区文成大道零售中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾叙州临时交付中心</t>
+          <t>理想汽车拉萨文成大道零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州拱墅区城西银泰城零售中心</t>
+          <t>理想汽车海口万象城零售中心（新）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州城西银泰城零售中心</t>
+          <t>理想汽车海口万象城零售中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -15002,22 +15002,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东中山大信新都汇</t>
+          <t>濮阳德宇4S中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省中山市小榄大信新都汇</t>
+          <t>濮阳德宇维修中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨市城关区文成大道零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心（新址）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车拉萨文成大道零售中心</t>
+          <t>理想汽车泉州浦西万达零售中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
